--- a/metadata/plate_metadata/20260324_cep290_30hpf_plate02_well_metadata.xlsx
+++ b/metadata/plate_metadata/20260324_cep290_30hpf_plate02_well_metadata.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I2" s="8" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -973,17 +973,17 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1256,6 +1256,18 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="H22" s="9" t="n"/>
     </row>
